--- a/output/roomself_excel/9694.xlsx
+++ b/output/roomself_excel/9694.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49454</v>
+        <v>97548</v>
       </c>
       <c r="D2" t="n">
-        <v>1884</v>
+        <v>2796</v>
       </c>
       <c r="E2" t="n">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="F2" t="n">
-        <v>174</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95106</v>
+        <v>128478</v>
       </c>
       <c r="D3" t="n">
-        <v>2500</v>
+        <v>2884</v>
       </c>
       <c r="E3" t="n">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="F3" t="n">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18984</v>
+        <v>71474</v>
       </c>
       <c r="D4" t="n">
-        <v>1124</v>
+        <v>2188</v>
       </c>
       <c r="E4" t="n">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>235960</v>
+        <v>180956</v>
       </c>
       <c r="D5" t="n">
-        <v>4136</v>
+        <v>5164</v>
       </c>
       <c r="E5" t="n">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F5" t="n">
-        <v>356</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>199952</v>
+        <v>69615</v>
       </c>
       <c r="D6" t="n">
-        <v>4028</v>
+        <v>2144</v>
       </c>
       <c r="E6" t="n">
-        <v>640</v>
+        <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>338</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>180956</v>
+        <v>12707</v>
       </c>
       <c r="D7" t="n">
-        <v>5164</v>
+        <v>912</v>
       </c>
       <c r="E7" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91079</v>
+        <v>11220</v>
       </c>
       <c r="D8" t="n">
-        <v>3568</v>
+        <v>848</v>
       </c>
       <c r="E8" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22528</v>
+        <v>18984</v>
       </c>
       <c r="D9" t="n">
-        <v>1296</v>
+        <v>1124</v>
       </c>
       <c r="E9" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>97548</v>
+        <v>60503</v>
       </c>
       <c r="D10" t="n">
-        <v>2796</v>
+        <v>2224</v>
       </c>
       <c r="E10" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -674,10 +674,10 @@
         <v>2324</v>
       </c>
       <c r="E11" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69615</v>
+        <v>48401</v>
       </c>
       <c r="D12" t="n">
-        <v>2144</v>
+        <v>2520</v>
       </c>
       <c r="E12" t="n">
-        <v>411</v>
+        <v>302</v>
       </c>
       <c r="F12" t="n">
-        <v>215</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>48401</v>
+        <v>49454</v>
       </c>
       <c r="D13" t="n">
-        <v>2520</v>
+        <v>1884</v>
       </c>
       <c r="E13" t="n">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12707</v>
+        <v>24378</v>
       </c>
       <c r="D14" t="n">
-        <v>912</v>
+        <v>1364</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24378</v>
+        <v>235960</v>
       </c>
       <c r="D15" t="n">
-        <v>1364</v>
+        <v>4136</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>726</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11220</v>
+        <v>95106</v>
       </c>
       <c r="D16" t="n">
-        <v>848</v>
+        <v>2500</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -800,15 +800,59 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>22528</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E17" t="n">
+        <v>166</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>30576</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1708</v>
+      </c>
+      <c r="E18" t="n">
+        <v>209</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>28914</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D19" t="n">
         <v>1364</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E19" t="n">
         <v>199</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>174</v>
       </c>
     </row>

--- a/output/roomself_excel/9694.xlsx
+++ b/output/roomself_excel/9694.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2796</v>
       </c>
-      <c r="E2" t="n">
-        <v>374</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>358</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>286</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>2884</v>
       </c>
-      <c r="E3" t="n">
-        <v>415</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>338</v>
+        <v>399</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>322</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>2188</v>
       </c>
-      <c r="E4" t="n">
-        <v>225</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>5164</v>
       </c>
-      <c r="E5" t="n">
-        <v>728</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>319</v>
+        <v>540</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>680</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>2144</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>221</v>
       </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,12 @@
       <c r="D7" t="n">
         <v>912</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,12 @@
       <c r="D8" t="n">
         <v>848</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +713,20 @@
       <c r="D9" t="n">
         <v>1124</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>168</v>
       </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +743,12 @@
       <c r="D10" t="n">
         <v>2224</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +765,12 @@
       <c r="D11" t="n">
         <v>2324</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +787,20 @@
       <c r="D12" t="n">
         <v>2520</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>302</v>
       </c>
-      <c r="F12" t="n">
-        <v>16</v>
-      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +817,27 @@
       <c r="D13" t="n">
         <v>1884</v>
       </c>
-      <c r="E13" t="n">
-        <v>329</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>174</v>
+        <v>158</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>313</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +855,20 @@
       <c r="D14" t="n">
         <v>1364</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>102</v>
       </c>
-      <c r="F14" t="n">
-        <v>16</v>
-      </c>
+      <c r="G14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +885,27 @@
       <c r="D15" t="n">
         <v>4136</v>
       </c>
-      <c r="E15" t="n">
-        <v>726</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>356</v>
+        <v>680</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>694</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -783,12 +923,20 @@
       <c r="D16" t="n">
         <v>2500</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>262</v>
       </c>
-      <c r="F16" t="n">
-        <v>16</v>
-      </c>
+      <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +953,20 @@
       <c r="D17" t="n">
         <v>1296</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>166</v>
       </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +983,20 @@
       <c r="D18" t="n">
         <v>1708</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>209</v>
       </c>
-      <c r="F18" t="n">
-        <v>16</v>
-      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,11 +1013,27 @@
       <c r="D19" t="n">
         <v>1364</v>
       </c>
-      <c r="E19" t="n">
-        <v>199</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>174</v>
+        <v>183</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>158</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
